--- a/data/nzd0543/nzd0543.xlsx
+++ b/data/nzd0543/nzd0543.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H428"/>
+  <dimension ref="A1:H429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13236,7 +13236,7 @@
         <v>250.1</v>
       </c>
       <c r="F428" t="n">
-        <v>221.83</v>
+        <v>184.69</v>
       </c>
       <c r="G428" t="n">
         <v>216.71</v>
@@ -13244,6 +13244,36 @@
       <c r="H428" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>272.03</v>
+      </c>
+      <c r="C429" t="n">
+        <v>252.12</v>
+      </c>
+      <c r="D429" t="n">
+        <v>245.77</v>
+      </c>
+      <c r="E429" t="n">
+        <v>251.37</v>
+      </c>
+      <c r="F429" t="n">
+        <v>165.79</v>
+      </c>
+      <c r="G429" t="n">
+        <v>215.95</v>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13258,7 +13288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B523"/>
+  <dimension ref="A1:B524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18491,6 +18521,16 @@
       </c>
       <c r="B523" t="n">
         <v>0.61</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>-0.42</v>
       </c>
     </row>
   </sheetData>
@@ -18659,28 +18699,28 @@
         <v>0.0317</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2600491346612403</v>
+        <v>-0.2625722225217775</v>
       </c>
       <c r="J2" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K2" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02993424674535894</v>
+        <v>0.03064406265232988</v>
       </c>
       <c r="M2" t="n">
-        <v>8.677684734805073</v>
+        <v>8.671938193536981</v>
       </c>
       <c r="N2" t="n">
-        <v>123.7032632392023</v>
+        <v>123.4753437085191</v>
       </c>
       <c r="O2" t="n">
-        <v>11.12219687108632</v>
+        <v>11.11194599107281</v>
       </c>
       <c r="P2" t="n">
-        <v>284.2641041349399</v>
+        <v>284.2900974120844</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18737,28 +18777,28 @@
         <v>0.0256</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4458740230519838</v>
+        <v>-0.4474528150181543</v>
       </c>
       <c r="J3" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K3" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08065351620999306</v>
+        <v>0.08156919674516061</v>
       </c>
       <c r="M3" t="n">
-        <v>8.738087981847315</v>
+        <v>8.725456415452063</v>
       </c>
       <c r="N3" t="n">
-        <v>126.6525502199607</v>
+        <v>126.3802563143354</v>
       </c>
       <c r="O3" t="n">
-        <v>11.25400152034647</v>
+        <v>11.24189736273799</v>
       </c>
       <c r="P3" t="n">
-        <v>267.3008011433583</v>
+        <v>267.3171115818503</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18815,28 +18855,28 @@
         <v>0.0259</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3094631470120401</v>
+        <v>-0.3059294167914864</v>
       </c>
       <c r="J4" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K4" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04256236070302732</v>
+        <v>0.04180872960144655</v>
       </c>
       <c r="M4" t="n">
-        <v>8.461183699358921</v>
+        <v>8.460419053392243</v>
       </c>
       <c r="N4" t="n">
-        <v>121.6494073657323</v>
+        <v>121.4932651842337</v>
       </c>
       <c r="O4" t="n">
-        <v>11.02947901606111</v>
+        <v>11.02239834084369</v>
       </c>
       <c r="P4" t="n">
-        <v>246.5347715630069</v>
+        <v>246.4984803501254</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18893,28 +18933,28 @@
         <v>0.0204</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3057894819837064</v>
+        <v>-0.2919059427501023</v>
       </c>
       <c r="J5" t="n">
+        <v>428</v>
+      </c>
+      <c r="K5" t="n">
         <v>427</v>
       </c>
-      <c r="K5" t="n">
-        <v>426</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.03189301357024776</v>
+        <v>0.02894499373913961</v>
       </c>
       <c r="M5" t="n">
-        <v>10.04707608552377</v>
+        <v>10.08320672066863</v>
       </c>
       <c r="N5" t="n">
-        <v>159.3932878683614</v>
+        <v>161.0217027134267</v>
       </c>
       <c r="O5" t="n">
-        <v>12.62510545969266</v>
+        <v>12.68943271834587</v>
       </c>
       <c r="P5" t="n">
-        <v>230.1540829625249</v>
+        <v>230.011313478553</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18971,28 +19011,28 @@
         <v>0.0161</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4442832445480021</v>
+        <v>-0.4780449666638988</v>
       </c>
       <c r="J6" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K6" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0492518237913131</v>
+        <v>0.05639489995755387</v>
       </c>
       <c r="M6" t="n">
-        <v>10.96052626271742</v>
+        <v>10.99252791643192</v>
       </c>
       <c r="N6" t="n">
-        <v>210.9271137816152</v>
+        <v>212.3255174454235</v>
       </c>
       <c r="O6" t="n">
-        <v>14.52332998253552</v>
+        <v>14.57139380585891</v>
       </c>
       <c r="P6" t="n">
-        <v>211.2252143231336</v>
+        <v>211.5753332324581</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19049,28 +19089,28 @@
         <v>0.016</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04971684052674785</v>
+        <v>-0.04861210105456534</v>
       </c>
       <c r="J7" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K7" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001167265775299353</v>
+        <v>0.001121957571503573</v>
       </c>
       <c r="M7" t="n">
-        <v>8.253631702021474</v>
+        <v>8.23913972130264</v>
       </c>
       <c r="N7" t="n">
-        <v>118.6495524477347</v>
+        <v>118.3849820457799</v>
       </c>
       <c r="O7" t="n">
-        <v>10.89263753402888</v>
+        <v>10.88048629638308</v>
       </c>
       <c r="P7" t="n">
-        <v>214.9402033024798</v>
+        <v>214.9288452626126</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19108,7 +19148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H428"/>
+  <dimension ref="A1:H429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37001,7 +37041,7 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>-46.54335306100452,169.61361909101282</t>
+          <t>-46.54328043283116,169.6131466685074</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
@@ -37012,6 +37052,48 @@
       <c r="H428" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>-46.54102417599431,169.61493617611853</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>-46.54159201659183,169.61451329278438</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>-46.54218636500999,169.61426288507053</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>-46.54280407400705,169.61416447910247</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>-46.54324347268377,169.61290626016392</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>-46.543948307110405,169.613374655292</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0543/nzd0543.xlsx
+++ b/data/nzd0543/nzd0543.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H429"/>
+  <dimension ref="A1:H431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13233,13 +13233,13 @@
         <v>250.62</v>
       </c>
       <c r="E428" t="n">
-        <v>250.1</v>
+        <v>241.02</v>
       </c>
       <c r="F428" t="n">
         <v>184.69</v>
       </c>
       <c r="G428" t="n">
-        <v>216.71</v>
+        <v>220.42</v>
       </c>
       <c r="H428" t="inlineStr">
         <is>
@@ -13250,30 +13250,90 @@
     <row r="429">
       <c r="A429" s="1" t="inlineStr">
         <is>
-          <t>2026-07-18 22:20:15+00:00</t>
+          <t>2026-08-28 22:14:25+00:00</t>
         </is>
       </c>
       <c r="B429" t="n">
-        <v>272.03</v>
+        <v>270.83</v>
       </c>
       <c r="C429" t="n">
-        <v>252.12</v>
+        <v>251.33</v>
       </c>
       <c r="D429" t="n">
-        <v>245.77</v>
+        <v>245.81</v>
       </c>
       <c r="E429" t="n">
-        <v>251.37</v>
+        <v>241.2</v>
       </c>
       <c r="F429" t="n">
-        <v>165.79</v>
+        <v>184.69</v>
       </c>
       <c r="G429" t="n">
-        <v>215.95</v>
+        <v>221.63</v>
       </c>
       <c r="H429" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>262.31</v>
+      </c>
+      <c r="C430" t="n">
+        <v>242.63</v>
+      </c>
+      <c r="D430" t="n">
+        <v>237.8</v>
+      </c>
+      <c r="E430" t="n">
+        <v>228.37</v>
+      </c>
+      <c r="F430" t="n">
+        <v>177.76</v>
+      </c>
+      <c r="G430" t="n">
+        <v>220.53</v>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>260.21</v>
+      </c>
+      <c r="C431" t="n">
+        <v>240.61</v>
+      </c>
+      <c r="D431" t="n">
+        <v>233.37</v>
+      </c>
+      <c r="E431" t="n">
+        <v>220.6</v>
+      </c>
+      <c r="F431" t="n">
+        <v>172.16</v>
+      </c>
+      <c r="G431" t="n">
+        <v>220.53</v>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13288,7 +13348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B524"/>
+  <dimension ref="A1:B527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18531,6 +18591,36 @@
       </c>
       <c r="B524" t="n">
         <v>-0.42</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -18699,28 +18789,28 @@
         <v>0.0317</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2625722225217775</v>
+        <v>-0.2783280002737422</v>
       </c>
       <c r="J2" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="K2" t="n">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03064406265232988</v>
+        <v>0.03433718332030278</v>
       </c>
       <c r="M2" t="n">
-        <v>8.671938193536981</v>
+        <v>8.72249741001329</v>
       </c>
       <c r="N2" t="n">
-        <v>123.4753437085191</v>
+        <v>124.1212762889899</v>
       </c>
       <c r="O2" t="n">
-        <v>11.11194599107281</v>
+        <v>11.14097286097538</v>
       </c>
       <c r="P2" t="n">
-        <v>284.2900974120844</v>
+        <v>284.4535991166598</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18777,28 +18867,28 @@
         <v>0.0256</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4474528150181543</v>
+        <v>-0.4608463258847998</v>
       </c>
       <c r="J3" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="K3" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08156919674516061</v>
+        <v>0.08641909727987962</v>
       </c>
       <c r="M3" t="n">
-        <v>8.725456415452063</v>
+        <v>8.750848521671102</v>
       </c>
       <c r="N3" t="n">
-        <v>126.3802563143354</v>
+        <v>126.6732499737755</v>
       </c>
       <c r="O3" t="n">
-        <v>11.24189736273799</v>
+        <v>11.25492114471601</v>
       </c>
       <c r="P3" t="n">
-        <v>267.3171115818503</v>
+        <v>267.4564451025407</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18855,28 +18945,28 @@
         <v>0.0259</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3059294167914864</v>
+        <v>-0.3084359706344574</v>
       </c>
       <c r="J4" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="K4" t="n">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04180872960144655</v>
+        <v>0.04289756313001358</v>
       </c>
       <c r="M4" t="n">
-        <v>8.460419053392243</v>
+        <v>8.432373397106213</v>
       </c>
       <c r="N4" t="n">
-        <v>121.4932651842337</v>
+        <v>120.9827067967767</v>
       </c>
       <c r="O4" t="n">
-        <v>11.02239834084369</v>
+        <v>10.99921391722048</v>
       </c>
       <c r="P4" t="n">
-        <v>246.4984803501254</v>
+        <v>246.5242407317076</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18933,28 +19023,28 @@
         <v>0.0204</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2919059427501023</v>
+        <v>-0.2985934100951423</v>
       </c>
       <c r="J5" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="K5" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02894499373913961</v>
+        <v>0.03095223496211241</v>
       </c>
       <c r="M5" t="n">
-        <v>10.08320672066863</v>
+        <v>10.01364557478507</v>
       </c>
       <c r="N5" t="n">
-        <v>161.0217027134267</v>
+        <v>158.2385947668946</v>
       </c>
       <c r="O5" t="n">
-        <v>12.68943271834587</v>
+        <v>12.5792922999227</v>
       </c>
       <c r="P5" t="n">
-        <v>230.011313478553</v>
+        <v>230.0794035464172</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19011,28 +19101,28 @@
         <v>0.0161</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4780449666638988</v>
+        <v>-0.491939093795889</v>
       </c>
       <c r="J6" t="n">
+        <v>430</v>
+      </c>
+      <c r="K6" t="n">
         <v>428</v>
       </c>
-      <c r="K6" t="n">
-        <v>426</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.05639489995755387</v>
+        <v>0.05999317259687509</v>
       </c>
       <c r="M6" t="n">
-        <v>10.99252791643192</v>
+        <v>11.00812506228044</v>
       </c>
       <c r="N6" t="n">
-        <v>212.3255174454235</v>
+        <v>211.9169495381338</v>
       </c>
       <c r="O6" t="n">
-        <v>14.57139380585891</v>
+        <v>14.55736753462431</v>
       </c>
       <c r="P6" t="n">
-        <v>211.5753332324581</v>
+        <v>211.7214911157519</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19089,28 +19179,28 @@
         <v>0.016</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04861210105456534</v>
+        <v>-0.03770120132561625</v>
       </c>
       <c r="J7" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="K7" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001121957571503573</v>
+        <v>0.0006801447157807061</v>
       </c>
       <c r="M7" t="n">
-        <v>8.23913972130264</v>
+        <v>8.247366142862145</v>
       </c>
       <c r="N7" t="n">
-        <v>118.3849820457799</v>
+        <v>118.2674852307019</v>
       </c>
       <c r="O7" t="n">
-        <v>10.88048629638308</v>
+        <v>10.87508552751204</v>
       </c>
       <c r="P7" t="n">
-        <v>214.9288452626126</v>
+        <v>214.8161115555718</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19148,7 +19238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H429"/>
+  <dimension ref="A1:H431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37036,7 +37126,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>-46.542801590595666,169.61414832475663</t>
+          <t>-46.542783835116474,169.61403282759034</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
@@ -37046,7 +37136,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>-46.54394979330731,169.61338432263977</t>
+          <t>-46.54395704828338,169.6134315145693</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -37058,42 +37148,126 @@
     <row r="429">
       <c r="A429" s="1" t="inlineStr">
         <is>
-          <t>2026-07-18 22:20:15+00:00</t>
+          <t>2026-08-28 22:14:25+00:00</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>-46.54102417599431,169.61493617611853</t>
+          <t>-46.541021829556584,169.61492091263315</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>-46.54159201659183,169.61451329278438</t>
+          <t>-46.54159047181921,169.61450324423149</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>-46.54218636500999,169.61426288507053</t>
+          <t>-46.54218644322729,169.6142633938632</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>-46.54280407400705,169.61416447910247</t>
+          <t>-46.542784187098455,169.61403511718092</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>-46.54324347268377,169.61290626016392</t>
+          <t>-46.54328043283116,169.6131466685074</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>-46.543948307110405,169.613374655292</t>
+          <t>-46.54395941445741,169.6134469060102</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>-46.54100516979104,169.61481254192788</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>-46.54157345970892,169.61439258299362</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>-46.54217078016625,169.61416150816146</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>-46.54275909849199,169.6138719203306</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>-46.543266880834906,169.6130585187404</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>-46.543957263390176,169.61343291379117</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>-46.54100106349528,169.61478583084957</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>-46.54156950975558,169.61436688924564</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>-46.542162117536066,169.61410515941736</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>-46.542743904423226,169.61377308646388</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>-46.543255929677926,169.61298728664016</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>-46.543957263390176,169.61343291379117</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
